--- a/연구코드/results/regression/gangnam/female/regression_results.xlsx
+++ b/연구코드/results/regression/gangnam/female/regression_results.xlsx
@@ -557,13 +557,13 @@
         <v>0.0523</v>
       </c>
       <c r="M2">
-        <v>0.7848000000000001</v>
+        <v>0.6886</v>
       </c>
       <c r="N2">
-        <v>0.1047</v>
+        <v>0.675</v>
       </c>
       <c r="O2">
-        <v>0.9846</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -604,13 +604,13 @@
         <v>0.0478</v>
       </c>
       <c r="M3">
-        <v>0.7801</v>
+        <v>0.6409</v>
       </c>
       <c r="N3">
-        <v>0.1152</v>
+        <v>0.7695</v>
       </c>
       <c r="O3">
-        <v>0.9754</v>
+        <v>0.6031</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -651,13 +651,13 @@
         <v>0.046</v>
       </c>
       <c r="M4">
-        <v>0.786</v>
+        <v>0.6683</v>
       </c>
       <c r="N4">
-        <v>0.1466</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="O4">
-        <v>0.9738</v>
+        <v>0.6615</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -698,13 +698,13 @@
         <v>0.0411</v>
       </c>
       <c r="M5">
-        <v>0.7765</v>
+        <v>0.6825</v>
       </c>
       <c r="N5">
-        <v>0.1521</v>
+        <v>0.7441</v>
       </c>
       <c r="O5">
-        <v>0.96</v>
+        <v>0.6646</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -745,13 +745,13 @@
         <v>0.0409</v>
       </c>
       <c r="M6">
-        <v>0.7836</v>
+        <v>0.679</v>
       </c>
       <c r="N6">
-        <v>0.1992</v>
+        <v>0.7487</v>
       </c>
       <c r="O6">
-        <v>0.9554</v>
+        <v>0.6585</v>
       </c>
     </row>
   </sheetData>
